--- a/jogos_2025-06-19.xlsx
+++ b/jogos_2025-06-19.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="107">
   <si>
     <t>Date</t>
   </si>
@@ -202,12 +202,12 @@
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
+    <t>Norway Toppserien</t>
+  </si>
+  <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
-    <t>Norway Toppserien</t>
-  </si>
-  <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
@@ -223,15 +223,18 @@
     <t>Inter Turku</t>
   </si>
   <si>
+    <t>Andijan</t>
+  </si>
+  <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
+    <t>Rosengard Women</t>
+  </si>
+  <si>
     <t>Kristianstad</t>
   </si>
   <si>
-    <t>Rosengard Women</t>
-  </si>
-  <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
     <t>Lillestrøm W</t>
   </si>
   <si>
@@ -244,54 +247,51 @@
     <t>Brann W</t>
   </si>
   <si>
-    <t>Neftchi</t>
-  </si>
-  <si>
     <t>Piteå Women</t>
   </si>
   <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
     <t>USM Khenchela</t>
   </si>
   <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
     <t>MC Oran</t>
   </si>
   <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>Mash'al</t>
-  </si>
-  <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
     <t>ES Sétif</t>
   </si>
   <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
     <t>Xorazm</t>
   </si>
   <si>
     <t>KTP</t>
   </si>
   <si>
+    <t>Qizilqum</t>
+  </si>
+  <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
+    <t>Vittsjö</t>
+  </si>
+  <si>
     <t>Linköping</t>
   </si>
   <si>
-    <t>Vittsjö</t>
-  </si>
-  <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
     <t>Bodø / Glimt W</t>
   </si>
   <si>
@@ -304,37 +304,31 @@
     <t>Røa Women</t>
   </si>
   <si>
-    <t>Buxoro</t>
-  </si>
-  <si>
     <t>Häcken W</t>
   </si>
   <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>ASO Chlef</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
+    <t>NC Magra</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
     <t>El Bayadh</t>
   </si>
   <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
     <t>USM Alger</t>
   </si>
   <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>NC Magra</t>
-  </si>
-  <si>
-    <t>Nasaf</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
     <t>US Biskra</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -704,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD21"/>
+  <dimension ref="A1:BD20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:56">
@@ -894,7 +888,7 @@
         <v>67</v>
       </c>
       <c r="F2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -909,16 +903,16 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L2">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="M2">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="N2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -930,73 +924,73 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AK2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AM2">
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO2">
         <v>-1</v>
@@ -1064,7 +1058,7 @@
         <v>68</v>
       </c>
       <c r="F3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1079,16 +1073,16 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L3">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M3">
-        <v>6.03</v>
+        <v>5.1</v>
       </c>
       <c r="N3">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="O3">
         <v>1.26</v>
@@ -1100,19 +1094,19 @@
         <v>4</v>
       </c>
       <c r="R3">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S3">
         <v>3.8</v>
       </c>
       <c r="T3">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="U3">
         <v>1.75</v>
       </c>
       <c r="V3">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="W3">
         <v>1.18</v>
@@ -1121,85 +1115,85 @@
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Z3">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AA3">
         <v>5.5</v>
       </c>
       <c r="AB3">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AC3">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AD3">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AE3">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AF3">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG3">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH3">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AI3">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AJ3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AK3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AL3">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AM3">
         <v>1.12</v>
       </c>
       <c r="AN3">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AO3">
         <v>-1</v>
       </c>
       <c r="AP3">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AQ3">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AR3">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AS3">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AT3">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AU3">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="AV3">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AW3">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AX3">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AY3">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AZ3">
         <v>0</v>
@@ -1222,10 +1216,10 @@
         <v>45827</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
         <v>65</v>
@@ -1234,7 +1228,7 @@
         <v>69</v>
       </c>
       <c r="F4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1249,43 +1243,43 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L4">
-        <v>1.31</v>
+        <v>1.64</v>
       </c>
       <c r="M4">
-        <v>4.46</v>
+        <v>3.4</v>
       </c>
       <c r="N4">
-        <v>6.32</v>
+        <v>5.2</v>
       </c>
       <c r="O4">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X4">
         <v>0</v>
@@ -1294,49 +1288,49 @@
         <v>0</v>
       </c>
       <c r="Z4">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.48</v>
+        <v>2.16</v>
       </c>
       <c r="AC4">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="AD4">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AK4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AL4">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO4">
         <v>-1</v>
@@ -1378,13 +1372,13 @@
         <v>0</v>
       </c>
       <c r="BB4">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BC4">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BD4" s="3">
-        <v>45827.54166666666</v>
+        <v>45827.5</v>
       </c>
     </row>
     <row r="5" spans="1:56">
@@ -1404,7 +1398,7 @@
         <v>70</v>
       </c>
       <c r="F5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1419,94 +1413,94 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L5">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC5">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AK5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AL5">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO5">
         <v>-1</v>
@@ -1548,10 +1542,10 @@
         <v>0</v>
       </c>
       <c r="BB5">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BC5">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="BD5" s="3">
         <v>45827.54166666666</v>
@@ -1574,7 +1568,7 @@
         <v>71</v>
       </c>
       <c r="F6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1589,94 +1583,94 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AK6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AO6">
         <v>-1</v>
@@ -1718,10 +1712,10 @@
         <v>0</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="BD6" s="3">
         <v>45827.54166666666</v>
@@ -1744,7 +1738,7 @@
         <v>72</v>
       </c>
       <c r="F7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1759,43 +1753,43 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X7">
         <v>0</v>
@@ -1804,49 +1798,49 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AK7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AO7">
         <v>-1</v>
@@ -1888,10 +1882,10 @@
         <v>0</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BD7" s="3">
         <v>45827.54166666666</v>
@@ -1905,7 +1899,7 @@
         <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s">
         <v>65</v>
@@ -1914,7 +1908,7 @@
         <v>73</v>
       </c>
       <c r="F8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1929,7 +1923,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2004,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AK8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2075,7 +2069,7 @@
         <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
         <v>65</v>
@@ -2084,7 +2078,7 @@
         <v>74</v>
       </c>
       <c r="F9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2099,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2174,10 +2168,10 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AK9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2245,7 +2239,7 @@
         <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
         <v>65</v>
@@ -2254,7 +2248,7 @@
         <v>75</v>
       </c>
       <c r="F10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2269,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2344,10 +2338,10 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AK10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2415,7 +2409,7 @@
         <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s">
         <v>65</v>
@@ -2424,7 +2418,7 @@
         <v>76</v>
       </c>
       <c r="F11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2439,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -2514,10 +2508,10 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AK11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2585,7 +2579,7 @@
         <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
         <v>65</v>
@@ -2594,7 +2588,7 @@
         <v>77</v>
       </c>
       <c r="F12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2609,10 +2603,10 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L12">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="M12">
         <v>5.4</v>
@@ -2639,7 +2633,7 @@
         <v>2.2</v>
       </c>
       <c r="U12">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V12">
         <v>4.75</v>
@@ -2660,43 +2654,43 @@
         <v>4.75</v>
       </c>
       <c r="AB12">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AC12">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AD12">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AE12">
         <v>1.57</v>
       </c>
       <c r="AF12">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG12">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AH12">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="AI12">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AK12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AL12">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AM12">
         <v>1.09</v>
       </c>
       <c r="AN12">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AO12">
         <v>-1</v>
@@ -2764,7 +2758,7 @@
         <v>78</v>
       </c>
       <c r="F13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2779,7 +2773,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -2854,10 +2848,10 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AK13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2934,7 +2928,7 @@
         <v>79</v>
       </c>
       <c r="F14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2949,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3024,10 +3018,10 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AK14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3104,7 +3098,7 @@
         <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3119,7 +3113,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -3194,10 +3188,10 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AK15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3274,7 +3268,7 @@
         <v>81</v>
       </c>
       <c r="F16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3289,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -3364,10 +3358,10 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AK16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3444,7 +3438,7 @@
         <v>82</v>
       </c>
       <c r="F17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3459,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -3534,10 +3528,10 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AK17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3605,16 +3599,16 @@
         <v>59</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E18" t="s">
         <v>83</v>
       </c>
       <c r="F18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3629,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -3704,10 +3698,10 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AK18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3784,7 +3778,7 @@
         <v>84</v>
       </c>
       <c r="F19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3799,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3874,10 +3868,10 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AK19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3954,23 +3948,23 @@
         <v>85</v>
       </c>
       <c r="F20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" t="s">
         <v>105</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20" t="s">
-        <v>107</v>
-      </c>
       <c r="L20">
         <v>0</v>
       </c>
@@ -4044,10 +4038,10 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AK20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4104,176 +4098,6 @@
         <v>0</v>
       </c>
       <c r="BD20" s="3">
-        <v>45827.79166666666</v>
-      </c>
-    </row>
-    <row r="21" spans="1:56">
-      <c r="A21" s="2">
-        <v>45827</v>
-      </c>
-      <c r="B21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" t="s">
-        <v>66</v>
-      </c>
-      <c r="E21" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" t="s">
-        <v>106</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21" t="s">
-        <v>107</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>0</v>
-      </c>
-      <c r="AG21">
-        <v>0</v>
-      </c>
-      <c r="AH21">
-        <v>0</v>
-      </c>
-      <c r="AI21">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK21" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>0</v>
-      </c>
-      <c r="AN21">
-        <v>0</v>
-      </c>
-      <c r="AO21">
-        <v>-1</v>
-      </c>
-      <c r="AP21">
-        <v>0</v>
-      </c>
-      <c r="AQ21">
-        <v>0</v>
-      </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
-      <c r="AS21">
-        <v>0</v>
-      </c>
-      <c r="AT21">
-        <v>0</v>
-      </c>
-      <c r="AU21">
-        <v>0</v>
-      </c>
-      <c r="AV21">
-        <v>0</v>
-      </c>
-      <c r="AW21">
-        <v>0</v>
-      </c>
-      <c r="AX21">
-        <v>0</v>
-      </c>
-      <c r="AY21">
-        <v>0</v>
-      </c>
-      <c r="AZ21">
-        <v>0</v>
-      </c>
-      <c r="BA21">
-        <v>0</v>
-      </c>
-      <c r="BB21">
-        <v>0</v>
-      </c>
-      <c r="BC21">
-        <v>0</v>
-      </c>
-      <c r="BD21" s="3">
         <v>45827.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-06-19.xlsx
+++ b/jogos_2025-06-19.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="86">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -193,12 +139,12 @@
     <t>14:00</t>
   </si>
   <si>
+    <t>Finland Veikkausliiga</t>
+  </si>
+  <si>
     <t>Uzbekistan Uzbekistan Super League</t>
   </si>
   <si>
-    <t>Finland Veikkausliiga</t>
-  </si>
-  <si>
     <t>Norway Toppserien</t>
   </si>
   <si>
@@ -208,76 +154,76 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Inter Turku</t>
+  </si>
+  <si>
     <t>Andijan</t>
   </si>
   <si>
     <t>Sogdiana</t>
   </si>
   <si>
-    <t>Inter Turku</t>
+    <t>Stabæk Women</t>
+  </si>
+  <si>
+    <t>Brann W</t>
+  </si>
+  <si>
+    <t>Kolbotn</t>
+  </si>
+  <si>
+    <t>Kristianstad</t>
+  </si>
+  <si>
+    <t>Rosengard Women</t>
+  </si>
+  <si>
+    <t>Lillestrøm W</t>
   </si>
   <si>
     <t>Vålerenga Women</t>
   </si>
   <si>
-    <t>Brann W</t>
-  </si>
-  <si>
-    <t>Stabæk Women</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
-    <t>Rosengard Women</t>
-  </si>
-  <si>
-    <t>Kristianstad</t>
-  </si>
-  <si>
-    <t>Kolbotn</t>
-  </si>
-  <si>
     <t>Piteå Women</t>
   </si>
   <si>
+    <t>KTP</t>
+  </si>
+  <si>
     <t>Qizilqum</t>
   </si>
   <si>
     <t>Xorazm</t>
   </si>
   <si>
-    <t>KTP</t>
+    <t>Lyn W</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>Linköping</t>
+  </si>
+  <si>
+    <t>Vittsjö</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
   </si>
   <si>
     <t>Hønefoss Women</t>
   </si>
   <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
-    <t>Lyn W</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>Vittsjö</t>
-  </si>
-  <si>
-    <t>Linköping</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
     <t>Häcken W</t>
   </si>
   <si>
     <t>complete</t>
   </si>
   <si>
-    <t>incomplete</t>
+    <t>['18', '44', '82', '61', '90+2']</t>
   </si>
   <si>
     <t>['77']</t>
@@ -286,30 +232,27 @@
     <t>['83']</t>
   </si>
   <si>
-    <t>['18', '44', '82', '61', '90+2']</t>
+    <t>['53', '68', '78', '86']</t>
+  </si>
+  <si>
+    <t>['6', '37', '40', '44', '9001']</t>
+  </si>
+  <si>
+    <t>['12', '43']</t>
+  </si>
+  <si>
+    <t>['65', '54', '90+4']</t>
+  </si>
+  <si>
+    <t>['25', '69']</t>
+  </si>
+  <si>
+    <t>['11', '42', '63', '89']</t>
   </si>
   <si>
     <t>['6', '58', '59', '66', '69', '74', '9003']</t>
   </si>
   <si>
-    <t>['6', '37', '40', '44', '9001']</t>
-  </si>
-  <si>
-    <t>['53', '68', '78', '86']</t>
-  </si>
-  <si>
-    <t>['11', '42', '63', '89']</t>
-  </si>
-  <si>
-    <t>['25', '69']</t>
-  </si>
-  <si>
-    <t>['65', '54', '90+4']</t>
-  </si>
-  <si>
-    <t>['12', '43']</t>
-  </si>
-  <si>
     <t>[]</t>
   </si>
   <si>
@@ -319,13 +262,16 @@
     <t>['81']</t>
   </si>
   <si>
+    <t>['5', '7', '16', '62', '9004']</t>
+  </si>
+  <si>
+    <t>['12']</t>
+  </si>
+  <si>
     <t>['45+3', '80']</t>
   </si>
   <si>
-    <t>['12']</t>
-  </si>
-  <si>
-    <t>['5', '7', '16', '62', '9004']</t>
+    <t>['45+1', '17', '66', '79', '83']</t>
   </si>
 </sst>
 </file>
@@ -689,10 +635,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD12"/>
+  <dimension ref="A1:AL12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -807,276 +753,168 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45827</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="F2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="L2">
-        <v>1.78</v>
+        <v>1.27</v>
       </c>
       <c r="M2">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="N2">
-        <v>3.8</v>
+        <v>11</v>
       </c>
       <c r="O2">
+        <v>1.26</v>
+      </c>
+      <c r="P2">
+        <v>16</v>
+      </c>
+      <c r="Q2">
+        <v>4</v>
+      </c>
+      <c r="R2">
+        <v>1.18</v>
+      </c>
+      <c r="S2">
+        <v>4.2</v>
+      </c>
+      <c r="T2">
+        <v>1.9</v>
+      </c>
+      <c r="U2">
         <v>1.8</v>
       </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>2.5</v>
-      </c>
-      <c r="R2">
-        <v>1.42</v>
-      </c>
-      <c r="S2">
-        <v>2.75</v>
-      </c>
-      <c r="T2">
-        <v>3.04</v>
-      </c>
-      <c r="U2">
-        <v>1.37</v>
-      </c>
       <c r="V2">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="X2">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="Z2">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AA2">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="AB2">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AC2">
+        <v>3.17</v>
+      </c>
+      <c r="AD2">
+        <v>1.99</v>
+      </c>
+      <c r="AE2">
+        <v>1.91</v>
+      </c>
+      <c r="AF2">
         <v>1.75</v>
-      </c>
-      <c r="AD2">
-        <v>3.6</v>
-      </c>
-      <c r="AE2">
-        <v>1.3</v>
-      </c>
-      <c r="AF2">
-        <v>1.91</v>
       </c>
       <c r="AG2">
         <v>1.9</v>
       </c>
       <c r="AH2">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="AI2">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AJ2" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="AK2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AL2">
-        <v>1.27</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>1.94</v>
-      </c>
-      <c r="AO2">
-        <v>14</v>
-      </c>
-      <c r="AP2">
-        <v>1.59</v>
-      </c>
-      <c r="AQ2">
-        <v>1.98</v>
-      </c>
-      <c r="AR2">
-        <v>2.53</v>
-      </c>
-      <c r="AS2">
-        <v>3.38</v>
-      </c>
-      <c r="AT2">
-        <v>4.65</v>
-      </c>
-      <c r="AU2">
-        <v>2.28</v>
-      </c>
-      <c r="AV2">
-        <v>1.77</v>
-      </c>
-      <c r="AW2">
-        <v>1.46</v>
-      </c>
-      <c r="AX2">
-        <v>1.25</v>
-      </c>
-      <c r="AY2">
-        <v>1.14</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>1.8</v>
-      </c>
-      <c r="BC2">
-        <v>2.5</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>79</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45827.5</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45827</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="L3">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="M3">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N3">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="O3">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -1085,335 +923,227 @@
         <v>2.5</v>
       </c>
       <c r="R3">
+        <v>1.42</v>
+      </c>
+      <c r="S3">
+        <v>2.75</v>
+      </c>
+      <c r="T3">
+        <v>3.04</v>
+      </c>
+      <c r="U3">
+        <v>1.37</v>
+      </c>
+      <c r="V3">
+        <v>7</v>
+      </c>
+      <c r="W3">
+        <v>1.05</v>
+      </c>
+      <c r="X3">
+        <v>1.04</v>
+      </c>
+      <c r="Y3">
+        <v>8.6</v>
+      </c>
+      <c r="Z3">
+        <v>1.28</v>
+      </c>
+      <c r="AA3">
+        <v>3.3</v>
+      </c>
+      <c r="AB3">
+        <v>2.05</v>
+      </c>
+      <c r="AC3">
+        <v>1.75</v>
+      </c>
+      <c r="AD3">
+        <v>3.6</v>
+      </c>
+      <c r="AE3">
         <v>1.3</v>
       </c>
-      <c r="S3">
-        <v>3.1</v>
-      </c>
-      <c r="T3">
-        <v>2.4</v>
-      </c>
-      <c r="U3">
-        <v>1.5</v>
-      </c>
-      <c r="V3">
-        <v>6</v>
-      </c>
-      <c r="W3">
-        <v>1.11</v>
-      </c>
-      <c r="X3">
-        <v>1</v>
-      </c>
-      <c r="Y3">
-        <v>11.9</v>
-      </c>
-      <c r="Z3">
-        <v>1.18</v>
-      </c>
-      <c r="AA3">
-        <v>4.3</v>
-      </c>
-      <c r="AB3">
-        <v>1.62</v>
-      </c>
-      <c r="AC3">
-        <v>2.15</v>
-      </c>
-      <c r="AD3">
-        <v>2.66</v>
-      </c>
-      <c r="AE3">
-        <v>1.45</v>
-      </c>
       <c r="AF3">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="AG3">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AH3">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AI3">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AJ3" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="AK3" t="s">
-        <v>98</v>
-      </c>
-      <c r="AL3">
-        <v>1.25</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>1.65</v>
-      </c>
-      <c r="AO3">
-        <v>9</v>
-      </c>
-      <c r="AP3">
-        <v>1.21</v>
-      </c>
-      <c r="AQ3">
-        <v>1.4</v>
-      </c>
-      <c r="AR3">
-        <v>1.84</v>
-      </c>
-      <c r="AS3">
-        <v>2.06</v>
-      </c>
-      <c r="AT3">
-        <v>2.57</v>
-      </c>
-      <c r="AU3">
-        <v>3.78</v>
-      </c>
-      <c r="AV3">
-        <v>2.72</v>
-      </c>
-      <c r="AW3">
-        <v>2.12</v>
-      </c>
-      <c r="AX3">
-        <v>1.71</v>
-      </c>
-      <c r="AY3">
-        <v>1.44</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>1.73</v>
-      </c>
-      <c r="BC3">
-        <v>2.5</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>80</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45827.5</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45827</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="F4" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="L4">
-        <v>1.27</v>
+        <v>1.77</v>
       </c>
       <c r="M4">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="N4">
-        <v>11</v>
+        <v>3.6</v>
       </c>
       <c r="O4">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="P4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="R4">
+        <v>1.3</v>
+      </c>
+      <c r="S4">
+        <v>3.1</v>
+      </c>
+      <c r="T4">
+        <v>2.4</v>
+      </c>
+      <c r="U4">
+        <v>1.5</v>
+      </c>
+      <c r="V4">
+        <v>6</v>
+      </c>
+      <c r="W4">
+        <v>1.11</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+      <c r="Y4">
+        <v>11.9</v>
+      </c>
+      <c r="Z4">
         <v>1.18</v>
       </c>
-      <c r="S4">
-        <v>4.2</v>
-      </c>
-      <c r="T4">
-        <v>1.9</v>
-      </c>
-      <c r="U4">
-        <v>1.8</v>
-      </c>
-      <c r="V4">
-        <v>3.7</v>
-      </c>
-      <c r="W4">
-        <v>1.22</v>
-      </c>
-      <c r="X4">
-        <v>1.01</v>
-      </c>
-      <c r="Y4">
-        <v>23</v>
-      </c>
-      <c r="Z4">
-        <v>1.11</v>
-      </c>
       <c r="AA4">
-        <v>6.5</v>
+        <v>4.3</v>
       </c>
       <c r="AB4">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AC4">
-        <v>3.17</v>
+        <v>2.15</v>
       </c>
       <c r="AD4">
-        <v>1.99</v>
+        <v>2.66</v>
       </c>
       <c r="AE4">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="AF4">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG4">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AH4">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="AI4">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AJ4" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AK4" t="s">
-        <v>98</v>
-      </c>
-      <c r="AL4">
-        <v>1.11</v>
-      </c>
-      <c r="AM4">
-        <v>1.12</v>
-      </c>
-      <c r="AN4">
-        <v>4.2</v>
-      </c>
-      <c r="AO4">
-        <v>6</v>
-      </c>
-      <c r="AP4">
-        <v>1.19</v>
-      </c>
-      <c r="AQ4">
-        <v>1.38</v>
-      </c>
-      <c r="AR4">
-        <v>1.65</v>
-      </c>
-      <c r="AS4">
-        <v>2</v>
-      </c>
-      <c r="AT4">
-        <v>2.55</v>
-      </c>
-      <c r="AU4">
-        <v>4.3</v>
-      </c>
-      <c r="AV4">
-        <v>3.05</v>
-      </c>
-      <c r="AW4">
-        <v>2.1</v>
-      </c>
-      <c r="AX4">
-        <v>1.7</v>
-      </c>
-      <c r="AY4">
-        <v>1.45</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>1.26</v>
-      </c>
-      <c r="BC4">
-        <v>4</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>79</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45827.5</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45827</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="F5" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="L5">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="M5">
-        <v>14</v>
+        <v>3.41</v>
       </c>
       <c r="N5">
-        <v>15</v>
+        <v>2.4</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -1455,16 +1185,16 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.1</v>
+        <v>1.76</v>
       </c>
       <c r="AC5">
-        <v>5.44</v>
+        <v>1.94</v>
       </c>
       <c r="AD5">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AF5">
         <v>0</v>
@@ -1473,93 +1203,39 @@
         <v>0</v>
       </c>
       <c r="AH5">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="AK5" t="s">
-        <v>98</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>0</v>
-      </c>
-      <c r="AO5">
-        <v>8</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>0</v>
-      </c>
-      <c r="BC5">
-        <v>0</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>81</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45827.54166666666</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45827</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" t="s">
         <v>61</v>
-      </c>
-      <c r="D6" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" t="s">
-        <v>79</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -1574,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="L6">
         <v>1.05</v>
@@ -1649,111 +1325,57 @@
         <v>1.6</v>
       </c>
       <c r="AJ6" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AK6" t="s">
-        <v>98</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>0</v>
-      </c>
-      <c r="AO6">
-        <v>6</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>1.11</v>
-      </c>
-      <c r="BC6">
-        <v>6.5</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>79</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45827.54166666666</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45827</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="F7" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="L7">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1795,10 +1417,10 @@
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC7">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1819,257 +1441,149 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AK7" t="s">
-        <v>100</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
-      </c>
-      <c r="AO7">
-        <v>-1</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7">
-        <v>0</v>
-      </c>
-      <c r="AV7">
-        <v>0</v>
-      </c>
-      <c r="AW7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0</v>
-      </c>
-      <c r="AY7">
-        <v>0</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>0</v>
-      </c>
-      <c r="BC7">
-        <v>0</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>82</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45827.54166666666</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45827</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" t="s">
         <v>63</v>
       </c>
-      <c r="E8" t="s">
-        <v>70</v>
-      </c>
-      <c r="F8" t="s">
-        <v>81</v>
-      </c>
       <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L8">
+        <v>1.23</v>
+      </c>
+      <c r="M8">
+        <v>4.9</v>
+      </c>
+      <c r="N8">
+        <v>8.67</v>
+      </c>
+      <c r="O8">
+        <v>1.32</v>
+      </c>
+      <c r="P8">
+        <v>18.5</v>
+      </c>
+      <c r="Q8">
+        <v>3.28</v>
+      </c>
+      <c r="R8">
+        <v>1.25</v>
+      </c>
+      <c r="S8">
+        <v>3.4</v>
+      </c>
+      <c r="T8">
+        <v>2.33</v>
+      </c>
+      <c r="U8">
+        <v>1.53</v>
+      </c>
+      <c r="V8">
+        <v>4.9</v>
+      </c>
+      <c r="W8">
+        <v>1.14</v>
+      </c>
+      <c r="X8">
+        <v>1.03</v>
+      </c>
+      <c r="Y8">
+        <v>15</v>
+      </c>
+      <c r="Z8">
+        <v>1.17</v>
+      </c>
+      <c r="AA8">
+        <v>4.6</v>
+      </c>
+      <c r="AB8">
+        <v>1.53</v>
+      </c>
+      <c r="AC8">
+        <v>2.3</v>
+      </c>
+      <c r="AD8">
+        <v>2.4</v>
+      </c>
+      <c r="AE8">
+        <v>1.5</v>
+      </c>
+      <c r="AF8">
+        <v>1.91</v>
+      </c>
+      <c r="AG8">
+        <v>1.69</v>
+      </c>
+      <c r="AH8">
         <v>4</v>
       </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>2</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" t="s">
-        <v>86</v>
-      </c>
-      <c r="L8">
-        <v>1.24</v>
-      </c>
-      <c r="M8">
-        <v>5.6</v>
-      </c>
-      <c r="N8">
-        <v>8.6</v>
-      </c>
-      <c r="O8">
-        <v>1.25</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>4.33</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>1.61</v>
-      </c>
-      <c r="AC8">
-        <v>2.17</v>
-      </c>
-      <c r="AD8">
-        <v>2.1</v>
-      </c>
-      <c r="AE8">
-        <v>1.65</v>
-      </c>
-      <c r="AF8">
-        <v>0</v>
-      </c>
-      <c r="AG8">
-        <v>0</v>
-      </c>
-      <c r="AH8">
-        <v>0</v>
-      </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ8" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="AK8" t="s">
-        <v>98</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>0</v>
-      </c>
-      <c r="AO8">
-        <v>13</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8">
-        <v>0</v>
-      </c>
-      <c r="AV8">
-        <v>0</v>
-      </c>
-      <c r="AW8">
-        <v>0</v>
-      </c>
-      <c r="AX8">
-        <v>0</v>
-      </c>
-      <c r="AY8">
-        <v>0</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>1.25</v>
-      </c>
-      <c r="BC8">
-        <v>4.33</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>83</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45827.54166666666</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45827</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="F9" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -2084,7 +1598,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="L9">
         <v>1.45</v>
@@ -2159,281 +1673,173 @@
         <v>1.14</v>
       </c>
       <c r="AJ9" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AK9" t="s">
-        <v>101</v>
-      </c>
-      <c r="AL9">
-        <v>1.22</v>
-      </c>
-      <c r="AM9">
-        <v>1.15</v>
-      </c>
-      <c r="AN9">
-        <v>2.5</v>
-      </c>
-      <c r="AO9">
-        <v>16</v>
-      </c>
-      <c r="AP9">
-        <v>0</v>
-      </c>
-      <c r="AQ9">
-        <v>0</v>
-      </c>
-      <c r="AR9">
-        <v>0</v>
-      </c>
-      <c r="AS9">
-        <v>2</v>
-      </c>
-      <c r="AT9">
-        <v>0</v>
-      </c>
-      <c r="AU9">
-        <v>0</v>
-      </c>
-      <c r="AV9">
-        <v>0</v>
-      </c>
-      <c r="AW9">
-        <v>0</v>
-      </c>
-      <c r="AX9">
-        <v>1.8</v>
-      </c>
-      <c r="AY9">
-        <v>0</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>1.39</v>
-      </c>
-      <c r="BC9">
-        <v>2.97</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>84</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45827.54166666666</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45827</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="L10">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M10">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="N10">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="O10">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="P10">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>3.28</v>
+        <v>4.33</v>
       </c>
       <c r="R10">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC10">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AD10">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AE10">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AF10">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AK10" t="s">
-        <v>102</v>
-      </c>
-      <c r="AL10">
-        <v>1.02</v>
-      </c>
-      <c r="AM10">
-        <v>1.11</v>
-      </c>
-      <c r="AN10">
-        <v>3.54</v>
-      </c>
-      <c r="AO10">
-        <v>7</v>
-      </c>
-      <c r="AP10">
-        <v>0</v>
-      </c>
-      <c r="AQ10">
-        <v>0</v>
-      </c>
-      <c r="AR10">
-        <v>0</v>
-      </c>
-      <c r="AS10">
-        <v>2</v>
-      </c>
-      <c r="AT10">
-        <v>0</v>
-      </c>
-      <c r="AU10">
-        <v>0</v>
-      </c>
-      <c r="AV10">
-        <v>0</v>
-      </c>
-      <c r="AW10">
-        <v>0</v>
-      </c>
-      <c r="AX10">
-        <v>1.8</v>
-      </c>
-      <c r="AY10">
-        <v>0</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>1.32</v>
-      </c>
-      <c r="BC10">
-        <v>3.28</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>79</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45827.54166666666</v>
       </c>
     </row>
-    <row r="11" spans="1:56">
+    <row r="11" spans="1:38">
       <c r="A11" s="2">
         <v>45827</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="F11" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -2475,16 +1881,16 @@
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF11">
         <v>0</v>
@@ -2493,108 +1899,54 @@
         <v>0</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ11" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AK11" t="s">
-        <v>103</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>0</v>
-      </c>
-      <c r="AO11">
-        <v>9</v>
-      </c>
-      <c r="AP11">
-        <v>0</v>
-      </c>
-      <c r="AQ11">
-        <v>0</v>
-      </c>
-      <c r="AR11">
-        <v>0</v>
-      </c>
-      <c r="AS11">
-        <v>0</v>
-      </c>
-      <c r="AT11">
-        <v>0</v>
-      </c>
-      <c r="AU11">
-        <v>0</v>
-      </c>
-      <c r="AV11">
-        <v>0</v>
-      </c>
-      <c r="AW11">
-        <v>0</v>
-      </c>
-      <c r="AX11">
-        <v>0</v>
-      </c>
-      <c r="AY11">
-        <v>0</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>0</v>
-      </c>
-      <c r="BC11">
-        <v>0</v>
-      </c>
-      <c r="BD11" s="3">
+        <v>79</v>
+      </c>
+      <c r="AL11" s="3">
         <v>45827.54166666666</v>
       </c>
     </row>
-    <row r="12" spans="1:56">
+    <row r="12" spans="1:38">
       <c r="A12" s="2">
         <v>45827</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="F12" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="L12">
         <v>9.25</v>
@@ -2669,66 +2021,12 @@
         <v>1.17</v>
       </c>
       <c r="AJ12" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="AK12" t="s">
-        <v>98</v>
-      </c>
-      <c r="AL12">
-        <v>1.18</v>
-      </c>
-      <c r="AM12">
-        <v>1.09</v>
-      </c>
-      <c r="AN12">
-        <v>1.06</v>
-      </c>
-      <c r="AO12">
-        <v>-1</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12">
-        <v>0</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="AY12">
-        <v>0</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>3.56</v>
-      </c>
-      <c r="BC12">
-        <v>1.27</v>
-      </c>
-      <c r="BD12" s="3">
+        <v>85</v>
+      </c>
+      <c r="AL12" s="3">
         <v>45827.58333333334</v>
       </c>
     </row>

--- a/jogos_2025-06-19.xlsx
+++ b/jogos_2025-06-19.xlsx
@@ -643,106 +643,106 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.04</v>
-      </c>
       <c r="W2" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="X2" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.6</v>
+        <v>2.66</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AJ2" t="n">
         <v>2.5</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,22 +772,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -798,65 +798,65 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.77</v>
+        <v>1.27</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="N3" t="n">
-        <v>3.6</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>2.46</v>
+        <v>1.67</v>
       </c>
       <c r="P3" t="n">
-        <v>2.17</v>
+        <v>2.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.95</v>
+        <v>7.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.15</v>
+        <v>3.17</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.66</v>
+        <v>1.99</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.45</v>
+        <v>1.91</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>['18', '44', '82', '61', '90+2']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.65</v>
+        <v>4.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.73</v>
+        <v>1.26</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45827.5</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="M4" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>11</v>
+        <v>3.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.67</v>
+        <v>2.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.92</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.5</v>
+        <v>4.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9</v>
+        <v>3.04</v>
       </c>
       <c r="U4" t="n">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="X4" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.17</v>
+        <v>1.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.99</v>
+        <v>3.6</v>
       </c>
       <c r="AB4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC4" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.75</v>
       </c>
       <c r="AD4" t="n">
         <v>1.9</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['18', '44', '82', '61', '90+2']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.2</v>
+        <v>1.94</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.26</v>
+        <v>1.8</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45827.5</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="N5" t="n">
-        <v>8.6</v>
+        <v>8.67</v>
       </c>
       <c r="O5" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['11', '42', '63', '89']</t>
+          <t>['65', '54', '90+4']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4.33</v>
+        <v>3.28</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45827.54166666666</v>
@@ -1159,22 +1159,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
         <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="M6" t="n">
-        <v>4.9</v>
+        <v>4.35</v>
       </c>
       <c r="N6" t="n">
-        <v>8.67</v>
+        <v>5.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.61</v>
+        <v>2.27</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="U6" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W6" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X6" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['65', '54', '90+4']</t>
+          <t>['25', '69']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>['45+3', '80']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.54</v>
+        <v>2.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3.28</v>
+        <v>2.97</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45827.54166666666</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="M7" t="n">
-        <v>4.35</v>
+        <v>5.6</v>
       </c>
       <c r="N7" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="P7" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.6</v>
+        <v>7.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['25', '69']</t>
+          <t>['11', '42', '63', '89']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['45+3', '80']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.97</v>
+        <v>4.33</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45827.54166666666</v>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1443,22 +1443,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.05</v>
+        <v>2.56</v>
       </c>
       <c r="M8" t="n">
-        <v>12</v>
+        <v>3.41</v>
       </c>
       <c r="N8" t="n">
-        <v>15</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1482,16 +1482,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.76</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.85</v>
+        <v>1.94</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1501,12 +1501,12 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['6', '37', '40', '44', '9001']</t>
+          <t>['53', '68', '78', '86']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AG8" t="n">
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45827.54166666666</v>
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['53', '68', '78', '86']</t>
+          <t>['12', '43']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>['5', '7', '16', '62', '9004']</t>
         </is>
       </c>
       <c r="AG9" t="n">
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1869,16 +1869,16 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1888,12 +1888,12 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['12', '43']</t>
+          <t>['6', '37', '40', '44', '9001']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['5', '7', '16', '62', '9004']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG11" t="n">
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45827.54166666666</v>
@@ -1933,109 +1933,109 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>2</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC12" t="n">
         <v>2</v>
       </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD12" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['25', '57']</t>
+          <t>['50', '90+2']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['23', '61']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.35</v>
+        <v>2.55</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.83</v>
+        <v>4.75</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45827.5625</v>
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.53</v>
+        <v>3.1</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>2.18</v>
       </c>
       <c r="O13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC13" t="n">
         <v>1.8</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['50', '90+2']</t>
+          <t>['25', '57']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23', '61']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.55</v>
+        <v>1.35</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="AJ13" t="n">
-        <v>4.75</v>
+        <v>1.83</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45827.5625</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.45</v>
+        <v>9.25</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="N14" t="n">
-        <v>2.9</v>
+        <v>1.28</v>
       </c>
       <c r="O14" t="n">
-        <v>3.05</v>
+        <v>7.5</v>
       </c>
       <c r="P14" t="n">
-        <v>1.93</v>
+        <v>2.49</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.38</v>
+        <v>1.74</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="U14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['45+1', '17', '66', '79', '83']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.27</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['31']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>2.25</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45827.58333333334</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>9.25</v>
+        <v>4.18</v>
       </c>
       <c r="M15" t="n">
-        <v>4.75</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
         <v>1.28</v>
       </c>
-      <c r="O15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>['45+1', '17', '66', '79', '83']</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AI15" t="n">
-        <v>3.56</v>
+        <v>2.05</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.27</v>
+        <v>1.87</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45827.58333333334</v>
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.18</v>
+        <v>2.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="O16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA16" t="n">
         <v>4.6</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45827.58333333334</v>
